--- a/time sheet/5.xlsx
+++ b/time sheet/5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aboelkheirmohamed/code/99/social/2/RECZ/time sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A1BEC43-3A4D-694D-8568-E931C1271249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7FEC14-C6D0-C84A-BEA1-0976CB8F69D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1100" windowWidth="27640" windowHeight="15840" xr2:uid="{96BD8107-EDA2-6D4B-B978-EEBB2A208FA2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>Project</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>requested by Vishal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">circales </t>
   </si>
 </sst>
 </file>
@@ -894,7 +897,7 @@
       </c>
       <c r="C5" s="4">
         <f>C46</f>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5">
         <v>400</v>
@@ -939,7 +942,7 @@
       </c>
       <c r="C8" s="10">
         <f>SUM(C5:C7)</f>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="10">
         <f>SUM(D5:D7)</f>
@@ -1123,9 +1126,13 @@
       <c r="B20" s="13">
         <v>46149</v>
       </c>
-      <c r="C20" s="14"/>
+      <c r="C20" s="14">
+        <v>1.5</v>
+      </c>
       <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>19</v>
+      </c>
       <c r="F20" s="16"/>
       <c r="I20" s="13">
         <v>46149</v>
@@ -1622,7 +1629,7 @@
       <c r="B46" s="23"/>
       <c r="C46" s="24">
         <f>SUM(C14:C44)</f>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D46" s="24" t="s">
         <v>13</v>

--- a/time sheet/5.xlsx
+++ b/time sheet/5.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aboelkheirmohamed/code/99/social/2/RECZ/time sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7FEC14-C6D0-C84A-BEA1-0976CB8F69D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E29D28-3A80-EF4C-9B40-3609AAC66086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1100" windowWidth="27640" windowHeight="15840" xr2:uid="{96BD8107-EDA2-6D4B-B978-EEBB2A208FA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>Project</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t xml:space="preserve">circales </t>
+  </si>
+  <si>
+    <t>sub screens for home</t>
   </si>
 </sst>
 </file>
@@ -456,22 +459,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -524,6 +518,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,13 +900,13 @@
       </c>
       <c r="C5" s="4">
         <f>C46</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="5">
         <v>400</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6">
+      <c r="E5" s="26"/>
+      <c r="F5" s="26">
         <f>D8</f>
         <v>400</v>
       </c>
@@ -912,7 +915,7 @@
       <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <f>J46</f>
         <v>0</v>
       </c>
@@ -920,8 +923,8 @@
         <f>K46</f>
         <v>0</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="2:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
@@ -933,36 +936,36 @@
       <c r="D7" s="5">
         <v>0</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="2:13" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="8">
         <f>SUM(C5:C7)</f>
-        <v>3</v>
-      </c>
-      <c r="D8" s="10">
+        <v>5</v>
+      </c>
+      <c r="D8" s="8">
         <f>SUM(D5:D7)</f>
         <v>400</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="25" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E12" s="12"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
@@ -997,656 +1000,656 @@
       </c>
     </row>
     <row r="14" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="13">
+      <c r="B14" s="10">
         <v>46143</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="I14" s="13">
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+      <c r="I14" s="10">
         <v>46143</v>
       </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14">
+      <c r="J14" s="11"/>
+      <c r="K14" s="11">
         <f>SUM(J14)*25</f>
         <v>0</v>
       </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="16"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="13"/>
     </row>
     <row r="15" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="13">
+      <c r="B15" s="10">
         <v>46144</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="I15" s="13">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
+      <c r="I15" s="10">
         <v>46144</v>
       </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14">
+      <c r="J15" s="11"/>
+      <c r="K15" s="11">
         <f t="shared" ref="K15:K44" si="0">SUM(J15)*25</f>
         <v>0</v>
       </c>
-      <c r="L15" s="15"/>
-      <c r="M15" s="16"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
     </row>
     <row r="16" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="13">
+      <c r="B16" s="10">
         <v>46145</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="16"/>
-      <c r="I16" s="13">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="13"/>
+      <c r="I16" s="10">
         <v>46145</v>
       </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="16"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="11"/>
+      <c r="M16" s="13"/>
     </row>
     <row r="17" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="13">
+      <c r="B17" s="10">
         <v>46146</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="16"/>
-      <c r="I17" s="13">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="13"/>
+      <c r="I17" s="10">
         <v>46146</v>
       </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="16"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="11"/>
+      <c r="M17" s="13"/>
     </row>
     <row r="18" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="13">
+      <c r="B18" s="10">
         <v>46147</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14" t="s">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="I18" s="13">
+      <c r="F18" s="13"/>
+      <c r="I18" s="10">
         <v>46147</v>
       </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="14" t="s">
+      <c r="J18" s="11"/>
+      <c r="K18" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="M18" s="16"/>
+      <c r="M18" s="13"/>
     </row>
     <row r="19" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="13">
+      <c r="B19" s="10">
         <v>46148</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="11">
         <v>1.5</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14" t="s">
+      <c r="D19" s="11"/>
+      <c r="E19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="10">
         <v>46148</v>
       </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="16"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="11"/>
+      <c r="M19" s="13"/>
     </row>
     <row r="20" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="13">
+      <c r="B20" s="10">
         <v>46149</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="11">
         <v>1.5</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="11"/>
+      <c r="E20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="I20" s="13">
+      <c r="F20" s="13"/>
+      <c r="I20" s="10">
         <v>46149</v>
       </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="16"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" s="13"/>
     </row>
     <row r="21" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="13">
+      <c r="B21" s="10">
         <v>46150</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="14">
+        <v>2</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="I21" s="10">
+        <v>46150</v>
+      </c>
+      <c r="J21" s="14"/>
+      <c r="K21" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14" t="s">
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="10">
+        <v>46151</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="15"/>
+      <c r="I22" s="10">
+        <v>46151</v>
+      </c>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="11"/>
+      <c r="M22" s="15"/>
+    </row>
+    <row r="23" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="10">
+        <v>46152</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="13"/>
+      <c r="I23" s="10">
+        <v>46152</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="11"/>
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="10">
+        <v>46153</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="13"/>
+      <c r="I24" s="10">
+        <v>46153</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="13"/>
+      <c r="I25" s="10">
+        <v>46154</v>
+      </c>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="11"/>
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="I26" s="10">
+        <v>46155</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="10">
+        <v>46156</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="13"/>
+      <c r="I27" s="10">
+        <v>46156</v>
+      </c>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="11"/>
+      <c r="M27" s="13"/>
+    </row>
+    <row r="28" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="13"/>
+      <c r="I28" s="10">
+        <v>46157</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="11"/>
+      <c r="M28" s="13"/>
+    </row>
+    <row r="29" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="10">
+        <v>46158</v>
+      </c>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="13"/>
+      <c r="I29" s="10">
+        <v>46158</v>
+      </c>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="11"/>
+      <c r="M29" s="13"/>
+    </row>
+    <row r="30" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="10">
+        <v>46159</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="13"/>
+      <c r="I30" s="10">
+        <v>46159</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="11"/>
+      <c r="M30" s="13"/>
+    </row>
+    <row r="31" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="13"/>
+      <c r="I31" s="10">
+        <v>46160</v>
+      </c>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="11"/>
+      <c r="M31" s="13"/>
+    </row>
+    <row r="32" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="13"/>
+      <c r="I32" s="10">
+        <v>46161</v>
+      </c>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="11"/>
+      <c r="M32" s="13"/>
+    </row>
+    <row r="33" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="13"/>
+      <c r="I33" s="10">
+        <v>46162</v>
+      </c>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="11"/>
+      <c r="M33" s="13"/>
+    </row>
+    <row r="34" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="10">
+        <v>46163</v>
+      </c>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="13"/>
+      <c r="I34" s="10">
+        <v>46163</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="11"/>
+      <c r="M34" s="13"/>
+    </row>
+    <row r="35" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="10">
+        <v>46164</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="13"/>
+      <c r="I35" s="10">
+        <v>46164</v>
+      </c>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="11"/>
+      <c r="M35" s="13"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B36" s="10">
+        <v>46165</v>
+      </c>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="13"/>
+      <c r="I36" s="10">
+        <v>46165</v>
+      </c>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="11"/>
+      <c r="M36" s="13"/>
+    </row>
+    <row r="37" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="10">
+        <v>46166</v>
+      </c>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="13"/>
+      <c r="I37" s="10">
+        <v>46166</v>
+      </c>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="11"/>
+      <c r="M37" s="13"/>
+    </row>
+    <row r="38" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="10">
+        <v>46167</v>
+      </c>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="13"/>
+      <c r="I38" s="10">
+        <v>46167</v>
+      </c>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="11"/>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="13"/>
+      <c r="I39" s="10">
+        <v>46168</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="11"/>
+      <c r="M39" s="13"/>
+    </row>
+    <row r="40" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="13"/>
+      <c r="I40" s="10">
+        <v>46169</v>
+      </c>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" s="13"/>
+    </row>
+    <row r="41" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="10">
+        <v>46170</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="13"/>
+      <c r="I41" s="10">
+        <v>46170</v>
+      </c>
+      <c r="J41" s="24"/>
+      <c r="K41" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="11"/>
+      <c r="M41" s="13"/>
+    </row>
+    <row r="42" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="10">
+        <v>46171</v>
+      </c>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="13"/>
+      <c r="I42" s="10">
+        <v>46171</v>
+      </c>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="11"/>
+      <c r="M42" s="13"/>
+    </row>
+    <row r="43" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="10">
+        <v>46172</v>
+      </c>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="13"/>
+      <c r="I43" s="10">
+        <v>46172</v>
+      </c>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="11"/>
+      <c r="M43" s="13"/>
+    </row>
+    <row r="44" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="13"/>
+      <c r="I44" s="10">
+        <v>46173</v>
+      </c>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="11"/>
+      <c r="M44" s="13"/>
+    </row>
+    <row r="45" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="16"/>
+      <c r="C45" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="I21" s="13">
-        <v>46150</v>
-      </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="14" t="s">
+      <c r="E45" s="18"/>
+      <c r="F45" s="19"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="18"/>
+      <c r="M45" s="19"/>
+    </row>
+    <row r="46" spans="2:13" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="20"/>
+      <c r="C46" s="21">
+        <f>SUM(C14:C44)</f>
+        <v>5</v>
+      </c>
+      <c r="D46" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M21" s="16"/>
-    </row>
-    <row r="22" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="13">
-        <v>46151</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="18"/>
-      <c r="I22" s="13">
-        <v>46151</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="18"/>
-    </row>
-    <row r="23" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="13">
-        <v>46152</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="16"/>
-      <c r="I23" s="13">
-        <v>46152</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="14"/>
-      <c r="M23" s="16"/>
-    </row>
-    <row r="24" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="13">
-        <v>46153</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="16"/>
-      <c r="I24" s="13">
-        <v>46153</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="16"/>
-    </row>
-    <row r="25" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="13">
-        <v>46154</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="16"/>
-      <c r="I25" s="13">
-        <v>46154</v>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="16"/>
-    </row>
-    <row r="26" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="13">
-        <v>46155</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="I26" s="13">
-        <v>46155</v>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="13">
-        <v>46156</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="16"/>
-      <c r="I27" s="13">
-        <v>46156</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="14"/>
-      <c r="M27" s="16"/>
-    </row>
-    <row r="28" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="13">
-        <v>46157</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="16"/>
-      <c r="I28" s="13">
-        <v>46157</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="14"/>
-      <c r="M28" s="16"/>
-    </row>
-    <row r="29" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="13">
-        <v>46158</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="16"/>
-      <c r="I29" s="13">
-        <v>46158</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="16"/>
-    </row>
-    <row r="30" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="13">
-        <v>46159</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="16"/>
-      <c r="I30" s="13">
-        <v>46159</v>
-      </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="14"/>
-      <c r="M30" s="16"/>
-    </row>
-    <row r="31" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="13">
-        <v>46160</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="16"/>
-      <c r="I31" s="13">
-        <v>46160</v>
-      </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="14"/>
-      <c r="M31" s="16"/>
-    </row>
-    <row r="32" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="13">
-        <v>46161</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="16"/>
-      <c r="I32" s="13">
-        <v>46161</v>
-      </c>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="14"/>
-      <c r="M32" s="16"/>
-    </row>
-    <row r="33" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="13">
-        <v>46162</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="16"/>
-      <c r="I33" s="13">
-        <v>46162</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="14"/>
-      <c r="M33" s="16"/>
-    </row>
-    <row r="34" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="13">
-        <v>46163</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="16"/>
-      <c r="I34" s="13">
-        <v>46163</v>
-      </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="14"/>
-      <c r="M34" s="16"/>
-    </row>
-    <row r="35" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="13">
-        <v>46164</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="16"/>
-      <c r="I35" s="13">
-        <v>46164</v>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="16"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B36" s="13">
-        <v>46165</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="16"/>
-      <c r="I36" s="13">
-        <v>46165</v>
-      </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="14"/>
-      <c r="M36" s="16"/>
-    </row>
-    <row r="37" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="13">
-        <v>46166</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="16"/>
-      <c r="I37" s="13">
-        <v>46166</v>
-      </c>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="14"/>
-      <c r="M37" s="16"/>
-    </row>
-    <row r="38" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="13">
-        <v>46167</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="16"/>
-      <c r="I38" s="13">
-        <v>46167</v>
-      </c>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="14"/>
-      <c r="M38" s="16"/>
-    </row>
-    <row r="39" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="13">
-        <v>46168</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="16"/>
-      <c r="I39" s="13">
-        <v>46168</v>
-      </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L39" s="14"/>
-      <c r="M39" s="16"/>
-    </row>
-    <row r="40" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="13">
-        <v>46169</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="16"/>
-      <c r="I40" s="13">
-        <v>46169</v>
-      </c>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="14"/>
-      <c r="M40" s="16"/>
-    </row>
-    <row r="41" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="13">
-        <v>46170</v>
-      </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="16"/>
-      <c r="I41" s="13">
-        <v>46170</v>
-      </c>
-      <c r="J41" s="27"/>
-      <c r="K41" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="14"/>
-      <c r="M41" s="16"/>
-    </row>
-    <row r="42" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="13">
-        <v>46171</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="16"/>
-      <c r="I42" s="13">
-        <v>46171</v>
-      </c>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L42" s="14"/>
-      <c r="M42" s="16"/>
-    </row>
-    <row r="43" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="13">
-        <v>46172</v>
-      </c>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="16"/>
-      <c r="I43" s="13">
-        <v>46172</v>
-      </c>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L43" s="14"/>
-      <c r="M43" s="16"/>
-    </row>
-    <row r="44" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="13">
-        <v>46173</v>
-      </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="16"/>
-      <c r="I44" s="13">
-        <v>46173</v>
-      </c>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L44" s="14"/>
-      <c r="M44" s="16"/>
-    </row>
-    <row r="45" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="19"/>
-      <c r="C45" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="21"/>
-      <c r="F45" s="22"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="K45" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="L45" s="21"/>
-      <c r="M45" s="22"/>
-    </row>
-    <row r="46" spans="2:13" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="23"/>
-      <c r="C46" s="24">
-        <f>SUM(C14:C44)</f>
-        <v>3</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="24"/>
-      <c r="F46" s="25"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="24">
+      <c r="E46" s="21"/>
+      <c r="F46" s="22"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="21">
         <f>SUM(J14:J44)</f>
         <v>0</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="21">
         <f>SUM(K14:K44)</f>
         <v>0</v>
       </c>
-      <c r="L46" s="24"/>
-      <c r="M46" s="25"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="22"/>
     </row>
     <row r="47" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="2:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/time sheet/5.xlsx
+++ b/time sheet/5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aboelkheirmohamed/code/99/social/2/RECZ/time sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E29D28-3A80-EF4C-9B40-3609AAC66086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1722D-015D-4344-B33A-F911F41D2C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1100" windowWidth="27640" windowHeight="15840" xr2:uid="{96BD8107-EDA2-6D4B-B978-EEBB2A208FA2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>Project</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>sub screens for home</t>
+  </si>
+  <si>
+    <t>buddies flow</t>
   </si>
 </sst>
 </file>
@@ -900,7 +903,7 @@
       </c>
       <c r="C5" s="4">
         <f>C46</f>
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="D5" s="5">
         <v>400</v>
@@ -945,7 +948,7 @@
       </c>
       <c r="C8" s="8">
         <f>SUM(C5:C7)</f>
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="D8" s="8">
         <f>SUM(D5:D7)</f>
@@ -1152,7 +1155,7 @@
       <c r="B21" s="10">
         <v>46150</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="11">
         <v>2</v>
       </c>
       <c r="D21" s="11"/>
@@ -1177,10 +1180,16 @@
       <c r="B22" s="10">
         <v>46151</v>
       </c>
-      <c r="C22" s="11"/>
+      <c r="C22" s="11">
+        <v>3.5</v>
+      </c>
       <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="15"/>
+      <c r="E22" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="I22" s="10">
         <v>46151</v>
       </c>
@@ -1632,7 +1641,7 @@
       <c r="B46" s="20"/>
       <c r="C46" s="21">
         <f>SUM(C14:C44)</f>
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>13</v>

--- a/time sheet/5.xlsx
+++ b/time sheet/5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aboelkheirmohamed/code/99/social/2/RECZ/time sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1722D-015D-4344-B33A-F911F41D2C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6174996D-EF0D-4C4F-8B9A-F8F6294D9120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1100" windowWidth="27640" windowHeight="15840" xr2:uid="{96BD8107-EDA2-6D4B-B978-EEBB2A208FA2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>Project</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>buddies flow</t>
+  </si>
+  <si>
+    <t>buddies screens</t>
+  </si>
+  <si>
+    <t>64 screens</t>
   </si>
 </sst>
 </file>
@@ -903,7 +909,7 @@
       </c>
       <c r="C5" s="4">
         <f>C46</f>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="D5" s="5">
         <v>400</v>
@@ -948,7 +954,7 @@
       </c>
       <c r="C8" s="8">
         <f>SUM(C5:C7)</f>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="D8" s="8">
         <f>SUM(D5:D7)</f>
@@ -1205,10 +1211,16 @@
       <c r="B23" s="10">
         <v>46152</v>
       </c>
-      <c r="C23" s="11"/>
+      <c r="C23" s="11">
+        <v>2</v>
+      </c>
       <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="13"/>
+      <c r="E23" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="I23" s="10">
         <v>46152</v>
       </c>
@@ -1641,7 +1653,7 @@
       <c r="B46" s="20"/>
       <c r="C46" s="21">
         <f>SUM(C14:C44)</f>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>13</v>

--- a/time sheet/5.xlsx
+++ b/time sheet/5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aboelkheirmohamed/code/99/social/2/RECZ/time sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6174996D-EF0D-4C4F-8B9A-F8F6294D9120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A819878D-CE07-1B40-A707-3C875EFBDE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1100" windowWidth="27640" windowHeight="15840" xr2:uid="{96BD8107-EDA2-6D4B-B978-EEBB2A208FA2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>Project</t>
   </si>
@@ -107,10 +107,16 @@
     <t>buddies flow</t>
   </si>
   <si>
-    <t>buddies screens</t>
-  </si>
-  <si>
     <t>64 screens</t>
+  </si>
+  <si>
+    <t>circales new flow</t>
+  </si>
+  <si>
+    <t>Explain new feature video</t>
+  </si>
+  <si>
+    <t>buddies screens finlaze</t>
   </si>
 </sst>
 </file>
@@ -909,7 +915,7 @@
       </c>
       <c r="C5" s="4">
         <f>C46</f>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5">
         <v>400</v>
@@ -954,7 +960,7 @@
       </c>
       <c r="C8" s="8">
         <f>SUM(C5:C7)</f>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="D8" s="8">
         <f>SUM(D5:D7)</f>
@@ -1216,10 +1222,10 @@
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>23</v>
       </c>
       <c r="I23" s="10">
         <v>46152</v>
@@ -1255,9 +1261,13 @@
       <c r="B25" s="10">
         <v>46154</v>
       </c>
-      <c r="C25" s="11"/>
+      <c r="C25" s="11">
+        <v>3</v>
+      </c>
       <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
+      <c r="E25" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="F25" s="13"/>
       <c r="I25" s="10">
         <v>46154</v>
@@ -1291,9 +1301,13 @@
       <c r="B27" s="10">
         <v>46156</v>
       </c>
-      <c r="C27" s="11"/>
+      <c r="C27" s="11">
+        <v>0.5</v>
+      </c>
       <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
+      <c r="E27" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="F27" s="13"/>
       <c r="I27" s="10">
         <v>46156</v>
@@ -1653,7 +1667,7 @@
       <c r="B46" s="20"/>
       <c r="C46" s="21">
         <f>SUM(C14:C44)</f>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>13</v>
